--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260930.xlsx
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,142,000</t>
+          <t>604,027,270</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>604,027,270</t>
+          <t>5,142,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
